--- a/椙山改修/261030_課題リスト.xlsx
+++ b/椙山改修/261030_課題リスト.xlsx
@@ -1309,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="101.1" customFormat="1" customHeight="1" s="98">
+    <row r="6" ht="114.1" customFormat="1" customHeight="1" s="98">
       <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
@@ -1357,15 +1357,14 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
             <t>・10/2 第3回分科会　理事長プレゼン日時は調整中。定例にて施主へ日程調整を依頼することとした
 ・10/9 第2回定例　SCより意匠分科会を経て内装プレゼンの日程調整を依頼
 ・同　SJより10/19・20・21で理事長の予定（1時間程度）を調整すると回答
-・10/9　完了</t>
+・10/9　完了
+・10/14　NSより内装プレゼンは10/21(水)11:00～に決定（分科会終了後に電話にて）</t>
           </r>
         </is>
       </c>
@@ -2492,7 +2491,7 @@
       <c r="P24" s="20" t="n"/>
       <c r="Q24" s="1" t="n"/>
     </row>
-    <row r="25" ht="49.05" customFormat="1" customHeight="1" s="98">
+    <row r="25" ht="62.05" customFormat="1" customHeight="1" s="98">
       <c r="A25" s="15" t="n">
         <v>20</v>
       </c>
@@ -2527,7 +2526,22 @@
       </c>
       <c r="L25" s="33" t="inlineStr">
         <is>
-          <t>・9/28 第1回分科会　SC（生技）より指示依頼。追加になるが後者を推奨</t>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">・9/28 第1回分科会　SC（生技）より指示依頼。追加になるが後者を推奨
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <color rgb="FFFF0000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>・10/14 第4回分科会　建具廻りの摺り付けが必要なため、SCにて解体範囲図に斫り範囲を記入して提出する</t>
+          </r>
         </is>
       </c>
       <c r="M25" s="153" t="n"/>
@@ -3282,61 +3296,147 @@
       <c r="P39" s="56" t="n"/>
       <c r="Q39" s="1" t="n"/>
     </row>
-    <row r="40" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="149" t="n"/>
-      <c r="I40" s="24" t="n"/>
-      <c r="J40" s="18" t="n"/>
-      <c r="K40" s="17" t="n"/>
-      <c r="L40" s="25" t="n"/>
-      <c r="M40" s="153" t="n"/>
-      <c r="N40" s="149" t="n"/>
-      <c r="O40" s="19" t="n"/>
-      <c r="P40" s="20" t="n"/>
+    <row r="40" ht="88" customFormat="1" customHeight="1" s="98">
+      <c r="A40" s="115" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="116" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C40" s="116" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D40" s="116" t="n"/>
+      <c r="E40" s="116" t="n"/>
+      <c r="F40" s="116" t="n"/>
+      <c r="G40" s="116" t="n"/>
+      <c r="H40" s="156" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I40" s="118" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J40" s="119" t="inlineStr">
+        <is>
+          <t>SSD（新設自動ドア）と外構ウッドデッキの取合い・手摺
+SC案：手摺を方立ラインに合わせ、手摺の外側のウッドデッキはなくしたい</t>
+        </is>
+      </c>
+      <c r="K40" s="120" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L40" s="121" t="inlineStr">
+        <is>
+          <t>・10/14 第4回分科会　前回打合せ内容を整理したイメージでOK。はね出しでできるのがベスト、無理ならば滑る機構で脚をつく
+・ウッドデッキの積載荷重3,500N/㎡が条件
+・手摺の内側ラインを方立の内側に合わせる。貫通部はウッドデッキの目地に合わせたい
+・ウッドデッキは手摺の外側も必要（根太の面まで）
+・立上りは不要。根太とウッドデッキの質感が違うなら立下げ、同じなら切りっぱなしで良い</t>
+        </is>
+      </c>
+      <c r="M40" s="157" t="n"/>
+      <c r="N40" s="156" t="n"/>
+      <c r="O40" s="146" t="n"/>
+      <c r="P40" s="123" t="n"/>
       <c r="Q40" s="1" t="n"/>
     </row>
     <row r="41" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A41" s="15" t="n"/>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="149" t="n"/>
-      <c r="I41" s="24" t="n"/>
-      <c r="J41" s="18" t="n"/>
-      <c r="K41" s="17" t="n"/>
-      <c r="L41" s="25" t="n"/>
-      <c r="M41" s="153" t="n"/>
-      <c r="N41" s="149" t="n"/>
-      <c r="O41" s="19" t="n"/>
-      <c r="P41" s="20" t="n"/>
+      <c r="A41" s="46" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C41" s="47" t="n"/>
+      <c r="D41" s="47" t="n"/>
+      <c r="E41" s="47" t="n"/>
+      <c r="F41" s="47" t="n"/>
+      <c r="G41" s="47" t="n"/>
+      <c r="H41" s="151" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I41" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J41" s="49" t="inlineStr">
+        <is>
+          <t>ガラリ部のルーバー貼付けは無しとしたい。また天井ルーバーが干渉する</t>
+        </is>
+      </c>
+      <c r="K41" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L41" s="50" t="inlineStr">
+        <is>
+          <t>・10/14 第4回分科会　ガラリの上のルーバーは無しとする
+・天井ルーバーの干渉は範囲を検討。裏から点検できない可能性も含めて現地確認・検討する</t>
+        </is>
+      </c>
+      <c r="M41" s="154" t="n"/>
+      <c r="N41" s="151" t="n"/>
+      <c r="O41" s="155" t="n"/>
+      <c r="P41" s="43" t="n"/>
       <c r="Q41" s="2" t="n"/>
     </row>
-    <row r="42" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A42" s="15" t="n"/>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="149" t="n"/>
-      <c r="I42" s="24" t="n"/>
-      <c r="J42" s="18" t="n"/>
-      <c r="K42" s="17" t="n"/>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="153" t="n"/>
-      <c r="N42" s="149" t="n"/>
-      <c r="O42" s="19" t="n"/>
-      <c r="P42" s="20" t="n"/>
+    <row r="42" ht="49" customFormat="1" customHeight="1" s="98">
+      <c r="A42" s="46" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C42" s="47" t="n"/>
+      <c r="D42" s="47" t="n"/>
+      <c r="E42" s="47" t="n"/>
+      <c r="F42" s="47" t="n"/>
+      <c r="G42" s="47" t="n"/>
+      <c r="H42" s="151" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I42" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J42" s="49" t="inlineStr">
+        <is>
+          <t>西面の吸音ルーバーの下地がモルタルアートになっているが、施工時にモルタルアートが割れる可能性が高いため仕上変更をお願いしたい</t>
+        </is>
+      </c>
+      <c r="K42" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L42" s="50" t="inlineStr">
+        <is>
+          <t>・10/14 第4回分科会　西面のルーバー下地はタイル上を補修して塗装（EP-G）に変更
+・SCにてコスト増減を整理して伝える</t>
+        </is>
+      </c>
+      <c r="M42" s="154" t="n"/>
+      <c r="N42" s="151" t="n"/>
+      <c r="O42" s="155" t="n"/>
+      <c r="P42" s="43" t="n"/>
       <c r="Q42" s="1" t="n"/>
     </row>
     <row r="43" ht="40.05" customFormat="1" customHeight="1" s="98">
